--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_basneta_a_2023_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_basneta_a_2023_o_higgins.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:57</t>
+    <t xml:space="preserve">2026-09-24 01:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -845,19 +845,19 @@
         <v>25</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.4</v>
+        <v>0.01</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>33</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.36</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="16">
@@ -868,19 +868,19 @@
         <v>25</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.3</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>33</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.42</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="17">
@@ -891,19 +891,19 @@
         <v>25</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.08</v>
+        <v>0.12</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>33</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="18">
